--- a/labs/lab-13-performance-event-ingestion-attribution/data/performance_events.xlsx
+++ b/labs/lab-13-performance-event-ingestion-attribution/data/performance_events.xlsx
@@ -539,7 +539,7 @@
       </c>
       <c r="I2" t="inlineStr">
         <is>
-          <t>mock-api</t>
+          <t>socialpost-result-fixture</t>
         </is>
       </c>
     </row>
@@ -549,11 +549,7 @@
           <t>EVT-002</t>
         </is>
       </c>
-      <c r="B3" t="inlineStr">
-        <is>
-          <t>CMP-NS-001</t>
-        </is>
-      </c>
+      <c r="B3" t="inlineStr"/>
       <c r="C3" t="inlineStr">
         <is>
           <t>AST-001</t>
@@ -582,7 +578,7 @@
       </c>
       <c r="I3" t="inlineStr">
         <is>
-          <t>mock-crm</t>
+          <t>mock-crm-invalid</t>
         </is>
       </c>
     </row>
@@ -767,7 +763,7 @@
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>mock-api</t>
+          <t>socialpost-result-fixture</t>
         </is>
       </c>
     </row>
